--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N115_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N115_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>75.40474329274583</v>
+        <v>12.2532707850712</v>
       </c>
       <c r="D2" t="n">
-        <v>74.42278421094501</v>
+        <v>12.09370243427857</v>
       </c>
       <c r="E2" t="n">
-        <v>21.54432335697273</v>
+        <v>3.500952545508069</v>
       </c>
       <c r="F2" t="n">
-        <v>28.08095094492413</v>
+        <v>4.563154528550171</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.31609657880037</v>
+        <v>5.25136569405506</v>
       </c>
       <c r="D3" t="n">
-        <v>18.26088232109676</v>
+        <v>2.967393377178223</v>
       </c>
       <c r="E3" t="n">
-        <v>21.54432335697273</v>
+        <v>3.500952545508069</v>
       </c>
       <c r="F3" t="n">
-        <v>28.08095094492413</v>
+        <v>4.563154528550171</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
